--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487932_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487932_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1975</v>
+        <v>2.0057</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7371</v>
+        <v>1.2338</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4604</v>
+        <v>0.7719</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5324</v>
+        <v>1.5484</v>
       </c>
       <c r="H2" t="n">
-        <v>0.578</v>
+        <v>1.5247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9544</v>
+        <v>0.0237</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4671</v>
+        <v>1.8302</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0148</v>
+        <v>1.631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4523</v>
+        <v>0.1992</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0653</v>
+        <v>-0.2818</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5632</v>
+        <v>-0.1063</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5021</v>
+        <v>-0.1755</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2083</v>
+        <v>-0.7183</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2701</v>
+        <v>-0.0157</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9383</v>
+        <v>-0.7026</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1675</v>
+        <v>0.3432</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1675</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4465</v>
+        <v>1.5785</v>
       </c>
       <c r="E3" t="n">
-        <v>3.341</v>
+        <v>3.15</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8944</v>
+        <v>-1.5715</v>
       </c>
       <c r="G3" t="n">
         <v>1.7799</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.841</v>
+        <v>-0.709</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4501</v>
+        <v>0.2591</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2911</v>
+        <v>-0.9681</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1168</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1912</v>
+        <v>1.4555</v>
       </c>
       <c r="E4" t="n">
         <v>2.0155</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8243</v>
+        <v>-0.5601</v>
       </c>
       <c r="G4" t="n">
         <v>0.7045</v>
@@ -766,13 +766,13 @@
         <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0704</v>
+        <v>0.3347</v>
       </c>
       <c r="T4" t="n">
         <v>0.4005</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3301</v>
+        <v>-0.0659</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1824</v>
+        <v>1.2557</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6747</v>
+        <v>0.5881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.6677</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5484</v>
+        <v>1.5324</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5247</v>
+        <v>0.578</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0237</v>
+        <v>0.9544</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8302</v>
+        <v>0.4671</v>
       </c>
       <c r="K5" t="n">
-        <v>1.631</v>
+        <v>0.0148</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1992</v>
+        <v>0.4523</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2818</v>
+        <v>1.0653</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1063</v>
+        <v>0.5632</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1755</v>
+        <v>0.5021</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5416</v>
+        <v>0.2665</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5748</v>
+        <v>0.121</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9668</v>
+        <v>0.1456</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3432</v>
+        <v>-1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1168</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.276</v>
+        <v>0.1988</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.542</v>
+        <v>-1.1553</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2659</v>
+        <v>1.354</v>
       </c>
       <c r="G6" t="n">
         <v>1.7712</v>
@@ -922,13 +922,13 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5904</v>
+        <v>-0.1156</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4443</v>
+        <v>-0.0576</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1461</v>
+        <v>-0.058</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2836</v>
+        <v>0.1412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7288</v>
+        <v>0.0931</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0124</v>
+        <v>0.0481</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1762</v>
+        <v>0.3384</v>
       </c>
       <c r="H7" t="n">
-        <v>1.693</v>
+        <v>1.6292</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5168</v>
+        <v>-1.2908</v>
       </c>
       <c r="J7" t="n">
-        <v>1.956</v>
+        <v>0.2936</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7993</v>
+        <v>1.017</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1568</v>
+        <v>-0.7234</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7798</v>
+        <v>0.0448</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1063</v>
+        <v>0.6122</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6735</v>
+        <v>-0.5674</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3727</v>
+        <v>-0.1972</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8539</v>
+        <v>-0.2005</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5187</v>
+        <v>0.0033</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4151</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2283</v>
+        <v>0.3002</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1868</v>
+        <v>-1.2179</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3384</v>
+        <v>1.1762</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6292</v>
+        <v>1.693</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2908</v>
+        <v>-0.5168</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2936</v>
+        <v>1.956</v>
       </c>
       <c r="K8" t="n">
-        <v>1.017</v>
+        <v>1.7993</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7234</v>
+        <v>0.1568</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0448</v>
+        <v>-0.7798</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6122</v>
+        <v>-0.1063</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5674</v>
+        <v>-0.6735</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5219</v>
+        <v>0.4253</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2316</v>
+        <v>0.3132</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5868</v>
+        <v>-2.0689</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4757</v>
+        <v>-1.657</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1111</v>
+        <v>-0.412</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9892</v>
+        <v>-1.9647</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0412</v>
+        <v>-0.4478</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.948</v>
+        <v>-1.5169</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7642</v>
+        <v>-0.8011</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1674</v>
+        <v>-0.2435</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5968</v>
+        <v>-0.5576</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.225</v>
+        <v>-1.1636</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8738</v>
+        <v>-0.2043</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3512</v>
+        <v>-0.9593</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2892</v>
+        <v>-0.8418</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5153</v>
+        <v>-0.0452</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7738</v>
+        <v>-0.7965</v>
       </c>
       <c r="V9" t="n">
-        <v>0.697</v>
+        <v>0.1132</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8137</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
         <v>-0.1168</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3858</v>
+        <v>-2.4302</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6803</v>
+        <v>-1.7319</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7056</v>
+        <v>-0.6983</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9647</v>
+        <v>-3.9892</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4478</v>
+        <v>-2.0412</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5169</v>
+        <v>-1.948</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8011</v>
+        <v>-1.7642</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2435</v>
+        <v>-1.1674</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5576</v>
+        <v>-0.5968</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1636</v>
+        <v>-2.225</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2043</v>
+        <v>-0.8738</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9593</v>
+        <v>-1.3512</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1587</v>
+        <v>0.4458</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.2591</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0901</v>
+        <v>0.1866</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1132</v>
+        <v>0.697</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>0.8137</v>
       </c>
       <c r="X10" t="n">
         <v>-0.1168</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4449</v>
+        <v>-2.9407</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3351</v>
+        <v>-0.9484</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1098</v>
+        <v>-1.9923</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0396</v>
@@ -1312,13 +1312,13 @@
         <v>1.6649</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8723</v>
+        <v>-0.3681</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5252</v>
+        <v>-0.1385</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.347</v>
+        <v>-0.2296</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1168</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3746</v>
+        <v>-1.7222</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2357</v>
+        <v>1.888099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.6105</v>
+        <v>-3.610399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8575000000000008</v>
+        <v>0.8575000000000004</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4908</v>
+        <v>5.490800000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-4.6332</v>
@@ -1366,13 +1366,13 @@
         <v>8.6153</v>
       </c>
       <c r="K12" t="n">
-        <v>7.0439</v>
+        <v>7.043899999999998</v>
       </c>
       <c r="L12" t="n">
         <v>1.571599999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.757800000000001</v>
+        <v>-7.7578</v>
       </c>
       <c r="N12" t="n">
         <v>-1.5531</v>
@@ -1381,7 +1381,7 @@
         <v>-6.2047</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001999999999993118</v>
+        <v>0.000199999999999978</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.406</v>
@@ -1390,10 +1390,10 @@
         <v>10.4058</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8169</v>
+        <v>-1.1645</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3552000000000001</v>
+        <v>1.0075</v>
       </c>
       <c r="U12" t="n">
         <v>-2.172</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.558</v>
+        <v>4.4238</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9461</v>
+        <v>2.8745</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6119</v>
+        <v>1.5493</v>
       </c>
       <c r="G13" t="n">
         <v>4.291</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6832</v>
+        <v>0.549</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3073</v>
+        <v>0.2358</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3758</v>
+        <v>0.3132</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1473</v>
+        <v>3.5862</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8215</v>
+        <v>3.143</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3258</v>
+        <v>0.4432</v>
       </c>
       <c r="G14" t="n">
         <v>2.979</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0398</v>
+        <v>0.3991</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1866</v>
+        <v>0.1348</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1468</v>
+        <v>0.2643</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8025</v>
+        <v>1.1788</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8918</v>
+        <v>2.2133</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0893</v>
+        <v>-1.0345</v>
       </c>
       <c r="G15" t="n">
         <v>0.5263</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.2663</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4848</v>
+        <v>-0.1633</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1578</v>
+        <v>-0.103</v>
       </c>
       <c r="V15" t="n">
         <v>1.7513</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4344</v>
+        <v>0.1897</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1091</v>
+        <v>-0.1393</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3252</v>
+        <v>0.3291</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.585</v>
+        <v>0.262</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8038</v>
+        <v>-1.6035</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2188</v>
+        <v>1.8655</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6176</v>
+        <v>0.695</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0392</v>
+        <v>1.3267</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0326</v>
+        <v>-0.433</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.147</v>
+        <v>-0.9719</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1796</v>
+        <v>0.5389</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8331</v>
+        <v>0.1359</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7268</v>
+        <v>0.2063</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1064</v>
+        <v>-0.0704</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0613</v>
+        <v>-0.1704</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3296</v>
+        <v>-0.3195</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2683</v>
+        <v>0.1491</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0059</v>
+        <v>-0.585</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2133</v>
+        <v>-0.8038</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2074</v>
+        <v>0.2188</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.6176</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7763</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7054</v>
+        <v>0.0392</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9349</v>
+        <v>0.0326</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4369</v>
+        <v>-0.147</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.498</v>
+        <v>0.1796</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9434</v>
+        <v>0.2284</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4005</v>
+        <v>0.2981</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5427999999999999</v>
+        <v>-0.0698</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1238</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1238</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4631</v>
+        <v>-0.2616</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0492</v>
+        <v>0.3296</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4139</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9328</v>
+        <v>-1.0059</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4627</v>
+        <v>-1.2133</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5299</v>
+        <v>0.2074</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5697</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2051</v>
+        <v>-0.7763</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7748</v>
+        <v>0.7054</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5025</v>
+        <v>-0.9349</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2576</v>
+        <v>-0.4369</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2449</v>
+        <v>-0.498</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4568</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1566</v>
+        <v>0.6204</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2948</v>
+        <v>0.4005</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1383</v>
+        <v>0.2199</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9376</v>
+        <v>0.1238</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.23</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0056</v>
+        <v>-0.2717</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1037</v>
+        <v>0.058</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09810000000000001</v>
+        <v>-0.3297</v>
       </c>
       <c r="G19" t="n">
-        <v>0.262</v>
+        <v>-0.9328</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6035</v>
+        <v>-1.4627</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8655</v>
+        <v>0.5299</v>
       </c>
       <c r="J19" t="n">
-        <v>0.695</v>
+        <v>0.5697</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6317</v>
+        <v>-0.2051</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3267</v>
+        <v>0.7748</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.433</v>
+        <v>-1.5025</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9719</v>
+        <v>-1.2576</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5389</v>
+        <v>-0.2449</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0595</v>
+        <v>0.3479</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7581</v>
+        <v>0.402</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3014</v>
+        <v>-0.0541</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3161</v>
+        <v>-1.1869</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5276</v>
+        <v>-0.9562</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7885</v>
+        <v>-0.2306</v>
       </c>
       <c r="G20" t="n">
         <v>-3.101</v>
@@ -2014,13 +2014,13 @@
         <v>2.0812</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2962</v>
+        <v>-0.167</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6178</v>
+        <v>0.1891</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.914</v>
+        <v>-0.3562</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8545</v>
+        <v>-1.2409</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3973</v>
+        <v>-0.7543</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4572</v>
+        <v>-0.4866</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1735</v>
@@ -2092,13 +2092,13 @@
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3053</v>
+        <v>0.3083</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3915</v>
+        <v>0.2515</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0861</v>
+        <v>0.0568</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1675</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9897</v>
+        <v>-3.158</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.41</v>
+        <v>-2.8386</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5797</v>
+        <v>-0.3194</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1176</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5441</v>
+        <v>0.3758</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6458</v>
+        <v>0.2172</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1017</v>
+        <v>0.1586</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3745</v>
+        <v>3.088999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>3.610299999999999</v>
+        <v>3.6105</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2359</v>
+        <v>-0.5213000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8574999999999986</v>
+        <v>-0.8574999999999995</v>
       </c>
       <c r="H23" t="n">
         <v>-5.4907</v>
@@ -2248,13 +2248,13 @@
         <v>10.4059</v>
       </c>
       <c r="S23" t="n">
-        <v>1.817</v>
+        <v>2.5315</v>
       </c>
       <c r="T23" t="n">
         <v>2.172</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3553</v>
+        <v>0.3593</v>
       </c>
       <c r="V23" t="n">
         <v>1.4152</v>
